--- a/Under_Enrolled_Audit_2026_27.xlsx
+++ b/Under_Enrolled_Audit_2026_27.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Under-Enrolled Summary'!$A$1:$K$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Under-Enrolled Summary'!$A$1:$M$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,11 +52,17 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -96,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -110,6 +116,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -120,6 +129,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -127,13 +139,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -499,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -510,9 +525,11 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="53" customWidth="1" min="9" max="9"/>
+    <col width="58" customWidth="1" min="9" max="9"/>
     <col width="29" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -568,6 +585,16 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Prev Year World Language</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Prev Year Elective</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Schedule Status</t>
         </is>
       </c>
@@ -613,50 +640,70 @@
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
           <t>INCOMPLETE</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>121287</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Elliott, Michael</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D3" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G3" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H3" s="8" t="n">
+      <c r="D3" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H3" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>English, Mathematics, Physical Education, Science, Social Studies, Theology, World Language</t>
         </is>
       </c>
-      <c r="J3" s="12" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>All core subjects present</t>
         </is>
       </c>
-      <c r="K3" s="13" t="inlineStr">
+      <c r="K3" s="14" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="L3" s="14" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
@@ -703,50 +750,70 @@
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
           <t>INCOMPLETE</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>109385</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Saliba, Georges</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H5" s="8" t="n">
+      <c r="D5" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>Engineering, English, Mathematics, Science, Social Studies, Theology, World Language</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>Physical Education</t>
         </is>
       </c>
-      <c r="K5" s="13" t="inlineStr">
+      <c r="K5" s="14" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="M5" s="15" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
@@ -793,50 +860,70 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
           <t>INCOMPLETE</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>121949</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Ferko, Lavdosh</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H7" s="8" t="n">
+      <c r="D7" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>English, Mathematics, Physical Education, Science, Social Studies, Theology, World Language</t>
         </is>
       </c>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t>All core subjects present</t>
         </is>
       </c>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="M7" s="15" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
@@ -876,57 +963,77 @@
           <t>English, Mathematics, Physical Education, Science, Social Studies, Theology</t>
         </is>
       </c>
-      <c r="J8" s="15" t="inlineStr">
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>World Language</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
           <t>INCOMPLETE</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>121320</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Kirby, Benjamin</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="11" t="n">
         <v>7.5</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="10" t="n">
         <v>5.5</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="11" t="n">
         <v>1.5</v>
       </c>
-      <c r="H9" s="8" t="n">
+      <c r="H9" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>English, Mathematics, Physical Education, Science, Social Studies, Theology</t>
         </is>
       </c>
-      <c r="J9" s="14" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t>World Language</t>
         </is>
       </c>
-      <c r="K9" s="13" t="inlineStr">
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="M9" s="15" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
@@ -973,50 +1080,70 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
           <t>INCOMPLETE</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>108153</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Vagnone, Tyler</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H11" s="8" t="n">
+      <c r="D11" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>Business, English, Mathematics, Science, Social Studies, Theology, World Language</t>
         </is>
       </c>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>All core subjects present</t>
         </is>
       </c>
-      <c r="K11" s="13" t="inlineStr">
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="M11" s="15" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
@@ -1063,50 +1190,70 @@
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
           <t>INCOMPLETE</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>106291</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Bonita, Andrew</t>
         </is>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D13" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G13" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H13" s="8" t="n">
+      <c r="D13" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H13" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>English, Mathematics, Physical Education, Science, Social Studies, Theology, World Language</t>
         </is>
       </c>
-      <c r="J13" s="12" t="inlineStr">
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t>All core subjects present</t>
         </is>
       </c>
-      <c r="K13" s="13" t="inlineStr">
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>333 Italian III H</t>
+        </is>
+      </c>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M13" s="15" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
@@ -1151,52 +1298,72 @@
           <t>All core subjects present</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="19" t="inlineStr">
+        <is>
+          <t>332 Italian III</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>106243</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Duran, Nicholas</t>
         </is>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G15" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H15" s="8" t="n">
+      <c r="D15" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>Communication Arts, Engineering, English, Mathematics, Physical Education, Science, Social Studies, Theology</t>
         </is>
       </c>
-      <c r="J15" s="12" t="inlineStr">
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t>All core subjects present</t>
         </is>
       </c>
-      <c r="K15" s="13" t="inlineStr">
+      <c r="K15" s="18" t="inlineStr">
+        <is>
+          <t>330 Spanish III</t>
+        </is>
+      </c>
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>2054 Digital Media</t>
+        </is>
+      </c>
+      <c r="M15" s="15" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
@@ -1241,52 +1408,72 @@
           <t>All core subjects present</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr">
+      <c r="K16" s="19" t="inlineStr">
+        <is>
+          <t>330 Spanish III</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>112088</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Helou, Ramsey</t>
         </is>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D17" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G17" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H17" s="8" t="n">
+      <c r="D17" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H17" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="I17" s="12" t="inlineStr">
         <is>
           <t>Business, Communication Arts, Computer Science, English, Mathematics, Social Studies, Theology</t>
         </is>
       </c>
-      <c r="J17" s="12" t="inlineStr">
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>All core subjects present</t>
         </is>
       </c>
-      <c r="K17" s="13" t="inlineStr">
+      <c r="K17" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L17" s="18" t="inlineStr">
+        <is>
+          <t>2034 TV/Film Production &amp; Editing I</t>
+        </is>
+      </c>
+      <c r="M17" s="15" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
@@ -1331,52 +1518,72 @@
           <t>All core subjects present</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr">
+      <c r="K18" s="19" t="inlineStr">
+        <is>
+          <t>331 Spanish III H</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>106232</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Nadler, Nathaniel</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="G19" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I19" s="12" t="inlineStr">
         <is>
           <t>English, Social Studies, Theology</t>
         </is>
       </c>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="J19" s="16" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="K19" s="13" t="inlineStr">
+      <c r="K19" s="18" t="inlineStr">
+        <is>
+          <t>351 AP Spanish</t>
+        </is>
+      </c>
+      <c r="L19" s="18" t="inlineStr">
+        <is>
+          <t>490 AP Computer Science A</t>
+        </is>
+      </c>
+      <c r="M19" s="15" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
@@ -1423,12 +1630,22 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
           <t>INCOMPLETE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K20"/>
+  <autoFilter ref="A1:M20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1446,7 +1663,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="53" customWidth="1" min="5" max="5"/>
+    <col width="57" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -1596,61 +1813,61 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>113184</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Bardales, Carlos</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>420</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Geometry</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H3" s="9" t="n">
+      <c r="H3" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I3" s="9" t="n">
+      <c r="I3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M3" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N3" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O3" s="9" t="n">
+      <c r="K3" s="9" t="inlineStr"/>
+      <c r="L3" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M3" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N3" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O3" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1714,61 +1931,61 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>113184</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Bardales, Carlos</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>520</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Chemistry</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H5" s="9" t="n">
+      <c r="H5" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M5" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N5" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O5" s="9" t="n">
+      <c r="K5" s="9" t="inlineStr"/>
+      <c r="L5" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M5" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N5" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O5" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1832,61 +2049,61 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>113184</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Bardales, Carlos</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>820</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Theology 10</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr"/>
-      <c r="L7" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M7" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N7" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O7" s="9" t="n">
+      <c r="K7" s="9" t="inlineStr"/>
+      <c r="L7" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N7" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O7" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1950,61 +2167,61 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>121287</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Elliott, Michael</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>122</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>American Literature</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr"/>
-      <c r="L9" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M9" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N9" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O9" s="9" t="n">
+      <c r="K9" s="9" t="inlineStr"/>
+      <c r="L9" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N9" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O9" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2068,61 +2285,61 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>121287</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Elliott, Michael</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>620</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>Driver's Ed/PE</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>Physical Education</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H11" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="H11" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>Physical Education</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr"/>
-      <c r="L11" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M11" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N11" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O11" s="9" t="n">
+      <c r="K11" s="9" t="inlineStr"/>
+      <c r="L11" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N11" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O11" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2186,61 +2403,61 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>121287</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Elliott, Michael</t>
         </is>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>U.S. History I</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H13" s="9" t="n">
+      <c r="H13" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="I13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr"/>
-      <c r="L13" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M13" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N13" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O13" s="9" t="n">
+      <c r="K13" s="9" t="inlineStr"/>
+      <c r="L13" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O13" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2304,61 +2521,61 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>121287</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Elliott, Michael</t>
         </is>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Spanish II</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>World Language</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H15" s="9" t="n">
+      <c r="H15" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="I15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>World Language</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M15" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N15" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O15" s="9" t="n">
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N15" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O15" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2422,61 +2639,61 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>117427</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Irving, Corey</t>
         </is>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>420</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>Geometry</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H17" s="9" t="n">
+      <c r="H17" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr"/>
-      <c r="L17" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M17" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N17" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O17" s="9" t="n">
+      <c r="K17" s="9" t="inlineStr"/>
+      <c r="L17" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M17" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N17" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O17" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2540,61 +2757,61 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>117427</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Irving, Corey</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>520</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>Chemistry</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H19" s="9" t="n">
+      <c r="H19" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="I19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr"/>
-      <c r="L19" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M19" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N19" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O19" s="9" t="n">
+      <c r="K19" s="9" t="inlineStr"/>
+      <c r="L19" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M19" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N19" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O19" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2658,61 +2875,61 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>117427</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Irving, Corey</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>820</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Theology 10</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H21" s="9" t="n">
+      <c r="H21" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I21" s="9" t="n">
+      <c r="I21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr"/>
-      <c r="L21" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M21" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N21" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O21" s="9" t="n">
+      <c r="K21" s="9" t="inlineStr"/>
+      <c r="L21" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M21" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N21" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O21" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2776,57 +2993,57 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>109385</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Saliba, Georges</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C23" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>580</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>Robotics Engineering</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H23" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I23" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J23" s="8" t="inlineStr"/>
-      <c r="K23" s="8" t="inlineStr"/>
-      <c r="L23" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M23" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N23" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O23" s="9" t="n">
+      <c r="H23" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J23" s="9" t="inlineStr"/>
+      <c r="K23" s="9" t="inlineStr"/>
+      <c r="L23" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N23" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O23" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2890,61 +3107,61 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>109385</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Saliba, Georges</t>
         </is>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>420</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>Geometry</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H25" s="9" t="n">
+      <c r="H25" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I25" s="9" t="n">
+      <c r="I25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="K25" s="8" t="inlineStr"/>
-      <c r="L25" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M25" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N25" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O25" s="9" t="n">
+      <c r="K25" s="9" t="inlineStr"/>
+      <c r="L25" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M25" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N25" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O25" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3008,61 +3225,61 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>109385</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Saliba, Georges</t>
         </is>
       </c>
-      <c r="C27" s="8" t="n">
+      <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>U.S. History I</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H27" s="9" t="n">
+      <c r="H27" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I27" s="9" t="n">
+      <c r="I27" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="K27" s="8" t="inlineStr"/>
-      <c r="L27" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M27" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N27" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O27" s="9" t="n">
+      <c r="K27" s="9" t="inlineStr"/>
+      <c r="L27" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M27" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N27" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O27" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3126,61 +3343,61 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>109385</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Saliba, Georges</t>
         </is>
       </c>
-      <c r="C29" s="8" t="n">
+      <c r="C29" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>327</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>Latin II H</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>World Language</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H29" s="9" t="n">
+      <c r="H29" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I29" s="9" t="n">
+      <c r="I29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="8" t="inlineStr">
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>World Language</t>
         </is>
       </c>
-      <c r="K29" s="8" t="inlineStr"/>
-      <c r="L29" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M29" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N29" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O29" s="9" t="n">
+      <c r="K29" s="9" t="inlineStr"/>
+      <c r="L29" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M29" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N29" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O29" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3244,61 +3461,61 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>113831</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>Sanchez, Cordero</t>
         </is>
       </c>
-      <c r="C31" s="8" t="n">
+      <c r="C31" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>421</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>Geometry H</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H31" s="9" t="n">
+      <c r="H31" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I31" s="9" t="n">
+      <c r="I31" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J31" s="8" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="K31" s="8" t="inlineStr"/>
-      <c r="L31" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M31" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N31" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O31" s="9" t="n">
+      <c r="K31" s="9" t="inlineStr"/>
+      <c r="L31" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M31" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N31" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O31" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3362,61 +3579,61 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>113831</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>Sanchez, Cordero</t>
         </is>
       </c>
-      <c r="C33" s="8" t="n">
+      <c r="C33" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>520</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>Chemistry</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H33" s="9" t="n">
+      <c r="H33" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I33" s="9" t="n">
+      <c r="I33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="8" t="inlineStr">
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="K33" s="8" t="inlineStr"/>
-      <c r="L33" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M33" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N33" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O33" s="9" t="n">
+      <c r="K33" s="9" t="inlineStr"/>
+      <c r="L33" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M33" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N33" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O33" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3480,61 +3697,61 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>113831</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>Sanchez, Cordero</t>
         </is>
       </c>
-      <c r="C35" s="8" t="n">
+      <c r="C35" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>820</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>Theology 10</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H35" s="9" t="n">
+      <c r="H35" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I35" s="9" t="n">
+      <c r="I35" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="8" t="inlineStr">
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="K35" s="8" t="inlineStr"/>
-      <c r="L35" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M35" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N35" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O35" s="9" t="n">
+      <c r="K35" s="9" t="inlineStr"/>
+      <c r="L35" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M35" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N35" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O35" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3598,61 +3815,61 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>121949</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>Ferko, Lavdosh</t>
         </is>
       </c>
-      <c r="C37" s="8" t="n">
+      <c r="C37" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>British Literature</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H37" s="9" t="n">
+      <c r="H37" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I37" s="9" t="n">
+      <c r="I37" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="8" t="inlineStr">
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="K37" s="8" t="inlineStr"/>
-      <c r="L37" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N37" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O37" s="9" t="n">
+      <c r="K37" s="9" t="inlineStr"/>
+      <c r="L37" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M37" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N37" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O37" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3716,57 +3933,57 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>121949</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>Ferko, Lavdosh</t>
         </is>
       </c>
-      <c r="C39" s="8" t="n">
+      <c r="C39" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>631</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>CPR-AED Training/PE</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
         <is>
           <t>Physical Education</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H39" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I39" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J39" s="8" t="inlineStr"/>
-      <c r="K39" s="8" t="inlineStr"/>
-      <c r="L39" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M39" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N39" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O39" s="9" t="n">
+      <c r="H39" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I39" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J39" s="9" t="inlineStr"/>
+      <c r="K39" s="9" t="inlineStr"/>
+      <c r="L39" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M39" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N39" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O39" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3830,61 +4047,61 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>121949</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>Ferko, Lavdosh</t>
         </is>
       </c>
-      <c r="C41" s="8" t="n">
+      <c r="C41" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>731</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>U.S. History II H</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H41" s="9" t="n">
+      <c r="H41" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I41" s="9" t="n">
+      <c r="I41" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J41" s="8" t="inlineStr">
+      <c r="J41" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="K41" s="8" t="inlineStr"/>
-      <c r="L41" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M41" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N41" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O41" s="9" t="n">
+      <c r="K41" s="9" t="inlineStr"/>
+      <c r="L41" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M41" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N41" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O41" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3948,61 +4165,61 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>121949</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>Ferko, Lavdosh</t>
         </is>
       </c>
-      <c r="C43" s="8" t="n">
+      <c r="C43" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>330</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>Spanish III</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="F43" s="9" t="inlineStr">
         <is>
           <t>World Language</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H43" s="9" t="n">
+      <c r="H43" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I43" s="9" t="n">
+      <c r="I43" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="8" t="inlineStr">
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>World Language</t>
         </is>
       </c>
-      <c r="K43" s="8" t="inlineStr"/>
-      <c r="L43" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M43" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N43" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O43" s="9" t="n">
+      <c r="K43" s="9" t="inlineStr"/>
+      <c r="L43" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M43" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N43" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O43" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4066,61 +4283,61 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>108187</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>Greig, Anthony</t>
         </is>
       </c>
-      <c r="C45" s="8" t="n">
+      <c r="C45" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>430</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>Algebra II/Trig</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="F45" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="G45" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H45" s="9" t="n">
+      <c r="H45" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I45" s="9" t="n">
+      <c r="I45" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J45" s="8" t="inlineStr">
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="K45" s="8" t="inlineStr"/>
-      <c r="L45" s="9" t="n">
+      <c r="K45" s="9" t="inlineStr"/>
+      <c r="L45" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="M45" s="9" t="n">
+      <c r="M45" s="10" t="n">
         <v>7.5</v>
       </c>
-      <c r="N45" s="9" t="n">
+      <c r="N45" s="10" t="n">
         <v>5.5</v>
       </c>
-      <c r="O45" s="9" t="n">
+      <c r="O45" s="10" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -4180,61 +4397,61 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>108187</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>Greig, Anthony</t>
         </is>
       </c>
-      <c r="C47" s="8" t="n">
+      <c r="C47" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D47" s="9" t="inlineStr">
         <is>
           <t>530</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
+      <c r="F47" s="9" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="G47" s="8" t="inlineStr">
+      <c r="G47" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H47" s="9" t="n">
+      <c r="H47" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I47" s="9" t="n">
+      <c r="I47" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J47" s="8" t="inlineStr">
+      <c r="J47" s="9" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="K47" s="8" t="inlineStr"/>
-      <c r="L47" s="9" t="n">
+      <c r="K47" s="9" t="inlineStr"/>
+      <c r="L47" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="M47" s="9" t="n">
+      <c r="M47" s="10" t="n">
         <v>7.5</v>
       </c>
-      <c r="N47" s="9" t="n">
+      <c r="N47" s="10" t="n">
         <v>5.5</v>
       </c>
-      <c r="O47" s="9" t="n">
+      <c r="O47" s="10" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -4298,61 +4515,61 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>108187</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>Greig, Anthony</t>
         </is>
       </c>
-      <c r="C49" s="8" t="n">
+      <c r="C49" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D49" s="9" t="inlineStr">
         <is>
           <t>830</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t>Theology 11</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr">
+      <c r="F49" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="G49" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H49" s="9" t="n">
+      <c r="H49" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I49" s="9" t="n">
+      <c r="I49" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J49" s="8" t="inlineStr">
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="K49" s="8" t="inlineStr"/>
-      <c r="L49" s="9" t="n">
+      <c r="K49" s="9" t="inlineStr"/>
+      <c r="L49" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="M49" s="9" t="n">
+      <c r="M49" s="10" t="n">
         <v>7.5</v>
       </c>
-      <c r="N49" s="9" t="n">
+      <c r="N49" s="10" t="n">
         <v>5.5</v>
       </c>
-      <c r="O49" s="9" t="n">
+      <c r="O49" s="10" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -4416,61 +4633,61 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>121320</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>Kirby, Benjamin</t>
         </is>
       </c>
-      <c r="C51" s="8" t="n">
+      <c r="C51" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>AP Precalculus</t>
         </is>
       </c>
-      <c r="F51" s="8" t="inlineStr">
+      <c r="F51" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="G51" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H51" s="9" t="n">
+      <c r="H51" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I51" s="9" t="n">
+      <c r="I51" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J51" s="8" t="inlineStr">
+      <c r="J51" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="K51" s="8" t="inlineStr"/>
-      <c r="L51" s="9" t="n">
+      <c r="K51" s="9" t="inlineStr"/>
+      <c r="L51" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="M51" s="9" t="n">
+      <c r="M51" s="10" t="n">
         <v>7.5</v>
       </c>
-      <c r="N51" s="9" t="n">
+      <c r="N51" s="10" t="n">
         <v>5.5</v>
       </c>
-      <c r="O51" s="9" t="n">
+      <c r="O51" s="10" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -4530,61 +4747,61 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>121320</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>Kirby, Benjamin</t>
         </is>
       </c>
-      <c r="C53" s="8" t="n">
+      <c r="C53" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D53" s="9" t="inlineStr">
         <is>
           <t>531</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="E53" s="9" t="inlineStr">
         <is>
           <t>Physics H</t>
         </is>
       </c>
-      <c r="F53" s="8" t="inlineStr">
+      <c r="F53" s="9" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="G53" s="8" t="inlineStr">
+      <c r="G53" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H53" s="9" t="n">
+      <c r="H53" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I53" s="9" t="n">
+      <c r="I53" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J53" s="8" t="inlineStr">
+      <c r="J53" s="9" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="K53" s="8" t="inlineStr"/>
-      <c r="L53" s="9" t="n">
+      <c r="K53" s="9" t="inlineStr"/>
+      <c r="L53" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="M53" s="9" t="n">
+      <c r="M53" s="10" t="n">
         <v>7.5</v>
       </c>
-      <c r="N53" s="9" t="n">
+      <c r="N53" s="10" t="n">
         <v>5.5</v>
       </c>
-      <c r="O53" s="9" t="n">
+      <c r="O53" s="10" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -4648,61 +4865,61 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>121320</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>Kirby, Benjamin</t>
         </is>
       </c>
-      <c r="C55" s="8" t="n">
+      <c r="C55" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="D55" s="9" t="inlineStr">
         <is>
           <t>830</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>Theology 11</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr">
+      <c r="F55" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="G55" s="8" t="inlineStr">
+      <c r="G55" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H55" s="9" t="n">
+      <c r="H55" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I55" s="9" t="n">
+      <c r="I55" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J55" s="8" t="inlineStr">
+      <c r="J55" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="K55" s="8" t="inlineStr"/>
-      <c r="L55" s="9" t="n">
+      <c r="K55" s="9" t="inlineStr"/>
+      <c r="L55" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="M55" s="9" t="n">
+      <c r="M55" s="10" t="n">
         <v>7.5</v>
       </c>
-      <c r="N55" s="9" t="n">
+      <c r="N55" s="10" t="n">
         <v>5.5</v>
       </c>
-      <c r="O55" s="9" t="n">
+      <c r="O55" s="10" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -4766,61 +4983,61 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>121986</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>Rodriguez, Blake</t>
         </is>
       </c>
-      <c r="C57" s="8" t="n">
+      <c r="C57" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D57" s="9" t="inlineStr">
         <is>
           <t>440</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
+      <c r="E57" s="9" t="inlineStr">
         <is>
           <t>Precalculus</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr">
+      <c r="F57" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="G57" s="8" t="inlineStr">
+      <c r="G57" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H57" s="9" t="n">
+      <c r="H57" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I57" s="9" t="n">
+      <c r="I57" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J57" s="8" t="inlineStr">
+      <c r="J57" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="K57" s="8" t="inlineStr"/>
-      <c r="L57" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M57" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N57" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O57" s="9" t="n">
+      <c r="K57" s="9" t="inlineStr"/>
+      <c r="L57" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M57" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N57" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O57" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4880,61 +5097,61 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>121986</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>Rodriguez, Blake</t>
         </is>
       </c>
-      <c r="C59" s="8" t="n">
+      <c r="C59" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D59" s="9" t="inlineStr">
         <is>
           <t>530</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="E59" s="9" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="F59" s="8" t="inlineStr">
+      <c r="F59" s="9" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="G59" s="8" t="inlineStr">
+      <c r="G59" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H59" s="9" t="n">
+      <c r="H59" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I59" s="9" t="n">
+      <c r="I59" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J59" s="8" t="inlineStr">
+      <c r="J59" s="9" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="K59" s="8" t="inlineStr"/>
-      <c r="L59" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M59" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N59" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O59" s="9" t="n">
+      <c r="K59" s="9" t="inlineStr"/>
+      <c r="L59" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M59" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N59" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O59" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4998,61 +5215,61 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>121986</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>Rodriguez, Blake</t>
         </is>
       </c>
-      <c r="C61" s="8" t="n">
+      <c r="C61" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
         <is>
           <t>830</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="E61" s="9" t="inlineStr">
         <is>
           <t>Theology 11</t>
         </is>
       </c>
-      <c r="F61" s="8" t="inlineStr">
+      <c r="F61" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="G61" s="8" t="inlineStr">
+      <c r="G61" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H61" s="9" t="n">
+      <c r="H61" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I61" s="9" t="n">
+      <c r="I61" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J61" s="8" t="inlineStr">
+      <c r="J61" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="K61" s="8" t="inlineStr"/>
-      <c r="L61" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M61" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N61" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O61" s="9" t="n">
+      <c r="K61" s="9" t="inlineStr"/>
+      <c r="L61" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M61" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N61" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O61" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -5116,57 +5333,57 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t>108153</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>Vagnone, Tyler</t>
         </is>
       </c>
-      <c r="C63" s="8" t="n">
+      <c r="C63" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D63" s="9" t="inlineStr">
         <is>
           <t>734</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="E63" s="9" t="inlineStr">
         <is>
           <t>Leadership, Entrepreneurship and Opportunity Program I</t>
         </is>
       </c>
-      <c r="F63" s="8" t="inlineStr">
+      <c r="F63" s="9" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="G63" s="8" t="inlineStr">
+      <c r="G63" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H63" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I63" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J63" s="8" t="inlineStr"/>
-      <c r="K63" s="8" t="inlineStr"/>
-      <c r="L63" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M63" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N63" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O63" s="9" t="n">
+      <c r="H63" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I63" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J63" s="9" t="inlineStr"/>
+      <c r="K63" s="9" t="inlineStr"/>
+      <c r="L63" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M63" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N63" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O63" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -5230,61 +5447,61 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>108153</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>Vagnone, Tyler</t>
         </is>
       </c>
-      <c r="C65" s="8" t="n">
+      <c r="C65" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D65" s="9" t="inlineStr">
         <is>
           <t>440</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr">
+      <c r="E65" s="9" t="inlineStr">
         <is>
           <t>Precalculus</t>
         </is>
       </c>
-      <c r="F65" s="8" t="inlineStr">
+      <c r="F65" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="G65" s="8" t="inlineStr">
+      <c r="G65" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H65" s="9" t="n">
+      <c r="H65" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I65" s="9" t="n">
+      <c r="I65" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J65" s="8" t="inlineStr">
+      <c r="J65" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="K65" s="8" t="inlineStr"/>
-      <c r="L65" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M65" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N65" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O65" s="9" t="n">
+      <c r="K65" s="9" t="inlineStr"/>
+      <c r="L65" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M65" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N65" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O65" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -5348,61 +5565,61 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A67" s="9" t="inlineStr">
         <is>
           <t>108153</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
         <is>
           <t>Vagnone, Tyler</t>
         </is>
       </c>
-      <c r="C67" s="8" t="n">
+      <c r="C67" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D67" s="8" t="inlineStr">
+      <c r="D67" s="9" t="inlineStr">
         <is>
           <t>730</t>
         </is>
       </c>
-      <c r="E67" s="8" t="inlineStr">
+      <c r="E67" s="9" t="inlineStr">
         <is>
           <t>U.S. History II</t>
         </is>
       </c>
-      <c r="F67" s="8" t="inlineStr">
+      <c r="F67" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="G67" s="8" t="inlineStr">
+      <c r="G67" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H67" s="9" t="n">
+      <c r="H67" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I67" s="9" t="n">
+      <c r="I67" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J67" s="8" t="inlineStr">
+      <c r="J67" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="K67" s="8" t="inlineStr"/>
-      <c r="L67" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M67" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N67" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O67" s="9" t="n">
+      <c r="K67" s="9" t="inlineStr"/>
+      <c r="L67" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M67" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N67" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O67" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -5466,61 +5683,61 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>108153</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>Vagnone, Tyler</t>
         </is>
       </c>
-      <c r="C69" s="8" t="n">
+      <c r="C69" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="D69" s="9" t="inlineStr">
         <is>
           <t>333</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
+      <c r="E69" s="9" t="inlineStr">
         <is>
           <t>Italian III H</t>
         </is>
       </c>
-      <c r="F69" s="8" t="inlineStr">
+      <c r="F69" s="9" t="inlineStr">
         <is>
           <t>World Language</t>
         </is>
       </c>
-      <c r="G69" s="8" t="inlineStr">
+      <c r="G69" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H69" s="9" t="n">
+      <c r="H69" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I69" s="9" t="n">
+      <c r="I69" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J69" s="8" t="inlineStr">
+      <c r="J69" s="9" t="inlineStr">
         <is>
           <t>World Language</t>
         </is>
       </c>
-      <c r="K69" s="8" t="inlineStr"/>
-      <c r="L69" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M69" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N69" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O69" s="9" t="n">
+      <c r="K69" s="9" t="inlineStr"/>
+      <c r="L69" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M69" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N69" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O69" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -5580,61 +5797,61 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="inlineStr">
+      <c r="A71" s="9" t="inlineStr">
         <is>
           <t>106800</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>Wagner, Liran</t>
         </is>
       </c>
-      <c r="C71" s="8" t="n">
+      <c r="C71" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="D71" s="9" t="inlineStr">
         <is>
           <t>139</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr">
+      <c r="E71" s="9" t="inlineStr">
         <is>
           <t>AP English Language</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
+      <c r="F71" s="9" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="G71" s="8" t="inlineStr">
+      <c r="G71" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H71" s="9" t="n">
+      <c r="H71" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I71" s="9" t="n">
+      <c r="I71" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J71" s="8" t="inlineStr">
+      <c r="J71" s="9" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="K71" s="8" t="inlineStr"/>
-      <c r="L71" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M71" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N71" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O71" s="9" t="n">
+      <c r="K71" s="9" t="inlineStr"/>
+      <c r="L71" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M71" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N71" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O71" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -5698,61 +5915,61 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
+      <c r="A73" s="9" t="inlineStr">
         <is>
           <t>106800</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B73" s="9" t="inlineStr">
         <is>
           <t>Wagner, Liran</t>
         </is>
       </c>
-      <c r="C73" s="8" t="n">
+      <c r="C73" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="D73" s="9" t="inlineStr">
         <is>
           <t>557</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
+      <c r="E73" s="9" t="inlineStr">
         <is>
           <t>AP Physics 1</t>
         </is>
       </c>
-      <c r="F73" s="8" t="inlineStr">
+      <c r="F73" s="9" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="G73" s="8" t="inlineStr">
+      <c r="G73" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H73" s="9" t="n">
+      <c r="H73" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I73" s="9" t="n">
+      <c r="I73" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J73" s="8" t="inlineStr">
+      <c r="J73" s="9" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="K73" s="8" t="inlineStr"/>
-      <c r="L73" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M73" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N73" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O73" s="9" t="n">
+      <c r="K73" s="9" t="inlineStr"/>
+      <c r="L73" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M73" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N73" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O73" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -5816,61 +6033,61 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="A75" s="9" t="inlineStr">
         <is>
           <t>106800</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B75" s="9" t="inlineStr">
         <is>
           <t>Wagner, Liran</t>
         </is>
       </c>
-      <c r="C75" s="8" t="n">
+      <c r="C75" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D75" s="9" t="inlineStr">
         <is>
           <t>830</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr">
+      <c r="E75" s="9" t="inlineStr">
         <is>
           <t>Theology 11</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr">
+      <c r="F75" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="G75" s="8" t="inlineStr">
+      <c r="G75" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H75" s="9" t="n">
+      <c r="H75" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I75" s="9" t="n">
+      <c r="I75" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J75" s="8" t="inlineStr">
+      <c r="J75" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="K75" s="8" t="inlineStr"/>
-      <c r="L75" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M75" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N75" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O75" s="9" t="n">
+      <c r="K75" s="9" t="inlineStr"/>
+      <c r="L75" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M75" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N75" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O75" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -5934,61 +6151,61 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+      <c r="A77" s="9" t="inlineStr">
         <is>
           <t>106291</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B77" s="9" t="inlineStr">
         <is>
           <t>Bonita, Andrew</t>
         </is>
       </c>
-      <c r="C77" s="8" t="n">
+      <c r="C77" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D77" s="9" t="inlineStr">
         <is>
           <t>149</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
+      <c r="E77" s="9" t="inlineStr">
         <is>
           <t>AP English Literature</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
+      <c r="F77" s="9" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="G77" s="8" t="inlineStr">
+      <c r="G77" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H77" s="9" t="n">
+      <c r="H77" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I77" s="9" t="n">
+      <c r="I77" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J77" s="8" t="inlineStr">
+      <c r="J77" s="9" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="K77" s="8" t="inlineStr"/>
-      <c r="L77" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M77" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N77" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O77" s="9" t="n">
+      <c r="K77" s="9" t="inlineStr"/>
+      <c r="L77" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M77" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N77" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O77" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6052,57 +6269,57 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+      <c r="A79" s="9" t="inlineStr">
         <is>
           <t>106291</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="9" t="inlineStr">
         <is>
           <t>Bonita, Andrew</t>
         </is>
       </c>
-      <c r="C79" s="8" t="n">
+      <c r="C79" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D79" s="9" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr">
+      <c r="E79" s="9" t="inlineStr">
         <is>
           <t>Nutrition &amp; Fitness/PE</t>
         </is>
       </c>
-      <c r="F79" s="8" t="inlineStr">
+      <c r="F79" s="9" t="inlineStr">
         <is>
           <t>Physical Education</t>
         </is>
       </c>
-      <c r="G79" s="8" t="inlineStr">
+      <c r="G79" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H79" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I79" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J79" s="8" t="inlineStr"/>
-      <c r="K79" s="8" t="inlineStr"/>
-      <c r="L79" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M79" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N79" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O79" s="9" t="n">
+      <c r="H79" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I79" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J79" s="9" t="inlineStr"/>
+      <c r="K79" s="9" t="inlineStr"/>
+      <c r="L79" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M79" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N79" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O79" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6166,57 +6383,57 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="inlineStr">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>106291</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B81" s="9" t="inlineStr">
         <is>
           <t>Bonita, Andrew</t>
         </is>
       </c>
-      <c r="C81" s="8" t="n">
+      <c r="C81" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D81" s="9" t="inlineStr">
         <is>
           <t>765</t>
         </is>
       </c>
-      <c r="E81" s="8" t="inlineStr">
+      <c r="E81" s="9" t="inlineStr">
         <is>
           <t>AP Macroeconomics</t>
         </is>
       </c>
-      <c r="F81" s="8" t="inlineStr">
+      <c r="F81" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="G81" s="8" t="inlineStr">
+      <c r="G81" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H81" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I81" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J81" s="8" t="inlineStr"/>
-      <c r="K81" s="8" t="inlineStr"/>
-      <c r="L81" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M81" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N81" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O81" s="9" t="n">
+      <c r="H81" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I81" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J81" s="9" t="inlineStr"/>
+      <c r="K81" s="9" t="inlineStr"/>
+      <c r="L81" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M81" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N81" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O81" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6276,61 +6493,61 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="inlineStr">
+      <c r="A83" s="9" t="inlineStr">
         <is>
           <t>106291</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B83" s="9" t="inlineStr">
         <is>
           <t>Bonita, Andrew</t>
         </is>
       </c>
-      <c r="C83" s="8" t="n">
+      <c r="C83" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D83" s="9" t="inlineStr">
         <is>
           <t>849</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
+      <c r="E83" s="9" t="inlineStr">
         <is>
           <t>Catholic Social Teaching</t>
         </is>
       </c>
-      <c r="F83" s="8" t="inlineStr">
+      <c r="F83" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="G83" s="8" t="inlineStr">
+      <c r="G83" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H83" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I83" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J83" s="8" t="inlineStr">
+      <c r="H83" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I83" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J83" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="K83" s="8" t="inlineStr"/>
-      <c r="L83" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M83" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N83" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O83" s="9" t="n">
+      <c r="K83" s="9" t="inlineStr"/>
+      <c r="L83" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M83" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N83" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O83" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6394,61 +6611,61 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="inlineStr">
+      <c r="A85" s="9" t="inlineStr">
         <is>
           <t>106291</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B85" s="9" t="inlineStr">
         <is>
           <t>Bonita, Andrew</t>
         </is>
       </c>
-      <c r="C85" s="8" t="n">
+      <c r="C85" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="D85" s="9" t="inlineStr">
         <is>
           <t>352</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
+      <c r="E85" s="9" t="inlineStr">
         <is>
           <t>AP Italian</t>
         </is>
       </c>
-      <c r="F85" s="8" t="inlineStr">
+      <c r="F85" s="9" t="inlineStr">
         <is>
           <t>World Language</t>
         </is>
       </c>
-      <c r="G85" s="8" t="inlineStr">
+      <c r="G85" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H85" s="9" t="n">
+      <c r="H85" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I85" s="9" t="n">
+      <c r="I85" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J85" s="8" t="inlineStr">
+      <c r="J85" s="9" t="inlineStr">
         <is>
           <t>World Language</t>
         </is>
       </c>
-      <c r="K85" s="8" t="inlineStr"/>
-      <c r="L85" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M85" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N85" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O85" s="9" t="n">
+      <c r="K85" s="9" t="inlineStr"/>
+      <c r="L85" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M85" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N85" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O85" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6512,57 +6729,57 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="inlineStr">
+      <c r="A87" s="9" t="inlineStr">
         <is>
           <t>107376</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B87" s="9" t="inlineStr">
         <is>
           <t>Carfello, Braydon</t>
         </is>
       </c>
-      <c r="C87" s="8" t="n">
+      <c r="C87" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D87" s="8" t="inlineStr">
+      <c r="D87" s="9" t="inlineStr">
         <is>
           <t>242</t>
         </is>
       </c>
-      <c r="E87" s="8" t="inlineStr">
+      <c r="E87" s="9" t="inlineStr">
         <is>
           <t>Studio Art II</t>
         </is>
       </c>
-      <c r="F87" s="8" t="inlineStr">
+      <c r="F87" s="9" t="inlineStr">
         <is>
           <t>Humanities</t>
         </is>
       </c>
-      <c r="G87" s="8" t="inlineStr">
+      <c r="G87" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H87" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I87" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J87" s="8" t="inlineStr"/>
-      <c r="K87" s="8" t="inlineStr"/>
-      <c r="L87" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M87" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N87" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O87" s="9" t="n">
+      <c r="H87" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I87" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J87" s="9" t="inlineStr"/>
+      <c r="K87" s="9" t="inlineStr"/>
+      <c r="L87" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M87" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N87" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O87" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6626,57 +6843,57 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="inlineStr">
+      <c r="A89" s="9" t="inlineStr">
         <is>
           <t>107376</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B89" s="9" t="inlineStr">
         <is>
           <t>Carfello, Braydon</t>
         </is>
       </c>
-      <c r="C89" s="8" t="n">
+      <c r="C89" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D89" s="8" t="inlineStr">
+      <c r="D89" s="9" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E89" s="8" t="inlineStr">
+      <c r="E89" s="9" t="inlineStr">
         <is>
           <t>Nutrition &amp; Fitness/PE</t>
         </is>
       </c>
-      <c r="F89" s="8" t="inlineStr">
+      <c r="F89" s="9" t="inlineStr">
         <is>
           <t>Physical Education</t>
         </is>
       </c>
-      <c r="G89" s="8" t="inlineStr">
+      <c r="G89" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H89" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I89" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J89" s="8" t="inlineStr"/>
-      <c r="K89" s="8" t="inlineStr"/>
-      <c r="L89" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M89" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N89" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O89" s="9" t="n">
+      <c r="H89" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I89" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J89" s="9" t="inlineStr"/>
+      <c r="K89" s="9" t="inlineStr"/>
+      <c r="L89" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M89" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N89" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O89" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6736,61 +6953,61 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="inlineStr">
+      <c r="A91" s="9" t="inlineStr">
         <is>
           <t>107376</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B91" s="9" t="inlineStr">
         <is>
           <t>Carfello, Braydon</t>
         </is>
       </c>
-      <c r="C91" s="8" t="n">
+      <c r="C91" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D91" s="8" t="inlineStr">
+      <c r="D91" s="9" t="inlineStr">
         <is>
           <t>751</t>
         </is>
       </c>
-      <c r="E91" s="8" t="inlineStr">
+      <c r="E91" s="9" t="inlineStr">
         <is>
           <t>American Government &amp; Politics</t>
         </is>
       </c>
-      <c r="F91" s="8" t="inlineStr">
+      <c r="F91" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="G91" s="8" t="inlineStr">
+      <c r="G91" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H91" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I91" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J91" s="8" t="inlineStr">
+      <c r="H91" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I91" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J91" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="K91" s="8" t="inlineStr"/>
-      <c r="L91" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M91" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N91" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O91" s="9" t="n">
+      <c r="K91" s="9" t="inlineStr"/>
+      <c r="L91" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M91" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N91" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O91" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6850,57 +7067,57 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="inlineStr">
+      <c r="A93" s="9" t="inlineStr">
         <is>
           <t>107376</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B93" s="9" t="inlineStr">
         <is>
           <t>Carfello, Braydon</t>
         </is>
       </c>
-      <c r="C93" s="8" t="n">
+      <c r="C93" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="D93" s="9" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="E93" s="8" t="inlineStr">
+      <c r="E93" s="9" t="inlineStr">
         <is>
           <t>Psychology</t>
         </is>
       </c>
-      <c r="F93" s="8" t="inlineStr">
+      <c r="F93" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="G93" s="8" t="inlineStr">
+      <c r="G93" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H93" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I93" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J93" s="8" t="inlineStr"/>
-      <c r="K93" s="8" t="inlineStr"/>
-      <c r="L93" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M93" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N93" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O93" s="9" t="n">
+      <c r="H93" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I93" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J93" s="9" t="inlineStr"/>
+      <c r="K93" s="9" t="inlineStr"/>
+      <c r="L93" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M93" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N93" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O93" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6964,61 +7181,61 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="inlineStr">
+      <c r="A95" s="9" t="inlineStr">
         <is>
           <t>107376</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B95" s="9" t="inlineStr">
         <is>
           <t>Carfello, Braydon</t>
         </is>
       </c>
-      <c r="C95" s="8" t="n">
+      <c r="C95" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D95" s="8" t="inlineStr">
+      <c r="D95" s="9" t="inlineStr">
         <is>
           <t>851</t>
         </is>
       </c>
-      <c r="E95" s="8" t="inlineStr">
+      <c r="E95" s="9" t="inlineStr">
         <is>
           <t>Spirituality of Vocation</t>
         </is>
       </c>
-      <c r="F95" s="8" t="inlineStr">
+      <c r="F95" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="G95" s="8" t="inlineStr">
+      <c r="G95" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H95" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I95" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J95" s="8" t="inlineStr">
+      <c r="H95" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I95" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J95" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="K95" s="8" t="inlineStr"/>
-      <c r="L95" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M95" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N95" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O95" s="9" t="n">
+      <c r="K95" s="9" t="inlineStr"/>
+      <c r="L95" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M95" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N95" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O95" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -7078,57 +7295,57 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="inlineStr">
+      <c r="A97" s="9" t="inlineStr">
         <is>
           <t>106243</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B97" s="9" t="inlineStr">
         <is>
           <t>Duran, Nicholas</t>
         </is>
       </c>
-      <c r="C97" s="8" t="n">
+      <c r="C97" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D97" s="8" t="inlineStr">
+      <c r="D97" s="9" t="inlineStr">
         <is>
           <t>595</t>
         </is>
       </c>
-      <c r="E97" s="8" t="inlineStr">
+      <c r="E97" s="9" t="inlineStr">
         <is>
           <t>Engineering Design</t>
         </is>
       </c>
-      <c r="F97" s="8" t="inlineStr">
+      <c r="F97" s="9" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="G97" s="8" t="inlineStr">
+      <c r="G97" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H97" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I97" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J97" s="8" t="inlineStr"/>
-      <c r="K97" s="8" t="inlineStr"/>
-      <c r="L97" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M97" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N97" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O97" s="9" t="n">
+      <c r="H97" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I97" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J97" s="9" t="inlineStr"/>
+      <c r="K97" s="9" t="inlineStr"/>
+      <c r="L97" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M97" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N97" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O97" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -7192,61 +7409,61 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="inlineStr">
+      <c r="A99" s="9" t="inlineStr">
         <is>
           <t>106243</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B99" s="9" t="inlineStr">
         <is>
           <t>Duran, Nicholas</t>
         </is>
       </c>
-      <c r="C99" s="8" t="n">
+      <c r="C99" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D99" s="8" t="inlineStr">
+      <c r="D99" s="9" t="inlineStr">
         <is>
           <t>440</t>
         </is>
       </c>
-      <c r="E99" s="8" t="inlineStr">
+      <c r="E99" s="9" t="inlineStr">
         <is>
           <t>Precalculus</t>
         </is>
       </c>
-      <c r="F99" s="8" t="inlineStr">
+      <c r="F99" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="G99" s="8" t="inlineStr">
+      <c r="G99" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H99" s="9" t="n">
+      <c r="H99" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I99" s="9" t="n">
+      <c r="I99" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J99" s="8" t="inlineStr">
+      <c r="J99" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="K99" s="8" t="inlineStr"/>
-      <c r="L99" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M99" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N99" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O99" s="9" t="n">
+      <c r="K99" s="9" t="inlineStr"/>
+      <c r="L99" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M99" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N99" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O99" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -7306,57 +7523,57 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="inlineStr">
+      <c r="A101" s="9" t="inlineStr">
         <is>
           <t>106243</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B101" s="9" t="inlineStr">
         <is>
           <t>Duran, Nicholas</t>
         </is>
       </c>
-      <c r="C101" s="8" t="n">
+      <c r="C101" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D101" s="8" t="inlineStr">
+      <c r="D101" s="9" t="inlineStr">
         <is>
           <t>544</t>
         </is>
       </c>
-      <c r="E101" s="8" t="inlineStr">
+      <c r="E101" s="9" t="inlineStr">
         <is>
           <t>Sports Medicine</t>
         </is>
       </c>
-      <c r="F101" s="8" t="inlineStr">
+      <c r="F101" s="9" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="G101" s="8" t="inlineStr">
+      <c r="G101" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H101" s="9" t="n">
+      <c r="H101" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I101" s="9" t="n">
+      <c r="I101" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J101" s="8" t="inlineStr"/>
-      <c r="K101" s="8" t="inlineStr"/>
-      <c r="L101" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M101" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N101" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O101" s="9" t="n">
+      <c r="J101" s="9" t="inlineStr"/>
+      <c r="K101" s="9" t="inlineStr"/>
+      <c r="L101" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M101" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N101" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O101" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -7416,57 +7633,57 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="8" t="inlineStr">
+      <c r="A103" s="9" t="inlineStr">
         <is>
           <t>106243</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B103" s="9" t="inlineStr">
         <is>
           <t>Duran, Nicholas</t>
         </is>
       </c>
-      <c r="C103" s="8" t="n">
+      <c r="C103" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D103" s="8" t="inlineStr">
+      <c r="D103" s="9" t="inlineStr">
         <is>
           <t>744</t>
         </is>
       </c>
-      <c r="E103" s="8" t="inlineStr">
+      <c r="E103" s="9" t="inlineStr">
         <is>
           <t>Sociology</t>
         </is>
       </c>
-      <c r="F103" s="8" t="inlineStr">
+      <c r="F103" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="G103" s="8" t="inlineStr">
+      <c r="G103" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H103" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I103" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J103" s="8" t="inlineStr"/>
-      <c r="K103" s="8" t="inlineStr"/>
-      <c r="L103" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M103" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N103" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O103" s="9" t="n">
+      <c r="H103" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I103" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J103" s="9" t="inlineStr"/>
+      <c r="K103" s="9" t="inlineStr"/>
+      <c r="L103" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M103" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N103" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O103" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -7530,61 +7747,61 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="8" t="inlineStr">
+      <c r="A105" s="9" t="inlineStr">
         <is>
           <t>106243</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B105" s="9" t="inlineStr">
         <is>
           <t>Duran, Nicholas</t>
         </is>
       </c>
-      <c r="C105" s="8" t="n">
+      <c r="C105" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D105" s="8" t="inlineStr">
+      <c r="D105" s="9" t="inlineStr">
         <is>
           <t>851</t>
         </is>
       </c>
-      <c r="E105" s="8" t="inlineStr">
+      <c r="E105" s="9" t="inlineStr">
         <is>
           <t>Spirituality of Vocation</t>
         </is>
       </c>
-      <c r="F105" s="8" t="inlineStr">
+      <c r="F105" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="G105" s="8" t="inlineStr">
+      <c r="G105" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H105" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I105" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J105" s="8" t="inlineStr">
+      <c r="H105" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I105" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J105" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="K105" s="8" t="inlineStr"/>
-      <c r="L105" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M105" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N105" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O105" s="9" t="n">
+      <c r="K105" s="9" t="inlineStr"/>
+      <c r="L105" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M105" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N105" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O105" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -7644,61 +7861,61 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="8" t="inlineStr">
+      <c r="A107" s="9" t="inlineStr">
         <is>
           <t>106323</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B107" s="9" t="inlineStr">
         <is>
           <t>Gebert, Evan</t>
         </is>
       </c>
-      <c r="C107" s="8" t="n">
+      <c r="C107" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D107" s="8" t="inlineStr">
+      <c r="D107" s="9" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="E107" s="8" t="inlineStr">
+      <c r="E107" s="9" t="inlineStr">
         <is>
           <t>College English Honors</t>
         </is>
       </c>
-      <c r="F107" s="8" t="inlineStr">
+      <c r="F107" s="9" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="G107" s="8" t="inlineStr">
+      <c r="G107" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H107" s="9" t="n">
+      <c r="H107" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I107" s="9" t="n">
+      <c r="I107" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J107" s="8" t="inlineStr">
+      <c r="J107" s="9" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="K107" s="8" t="inlineStr"/>
-      <c r="L107" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M107" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N107" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O107" s="9" t="n">
+      <c r="K107" s="9" t="inlineStr"/>
+      <c r="L107" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M107" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N107" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O107" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -7758,57 +7975,57 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="8" t="inlineStr">
+      <c r="A109" s="9" t="inlineStr">
         <is>
           <t>106323</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B109" s="9" t="inlineStr">
         <is>
           <t>Gebert, Evan</t>
         </is>
       </c>
-      <c r="C109" s="8" t="n">
+      <c r="C109" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D109" s="8" t="inlineStr">
+      <c r="D109" s="9" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="E109" s="8" t="inlineStr">
+      <c r="E109" s="9" t="inlineStr">
         <is>
           <t>Music Theory</t>
         </is>
       </c>
-      <c r="F109" s="8" t="inlineStr">
+      <c r="F109" s="9" t="inlineStr">
         <is>
           <t>Humanities</t>
         </is>
       </c>
-      <c r="G109" s="8" t="inlineStr">
+      <c r="G109" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H109" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I109" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J109" s="8" t="inlineStr"/>
-      <c r="K109" s="8" t="inlineStr"/>
-      <c r="L109" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M109" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N109" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O109" s="9" t="n">
+      <c r="H109" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I109" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J109" s="9" t="inlineStr"/>
+      <c r="K109" s="9" t="inlineStr"/>
+      <c r="L109" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M109" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N109" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O109" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -7872,57 +8089,57 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="8" t="inlineStr">
+      <c r="A111" s="9" t="inlineStr">
         <is>
           <t>106323</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B111" s="9" t="inlineStr">
         <is>
           <t>Gebert, Evan</t>
         </is>
       </c>
-      <c r="C111" s="8" t="n">
+      <c r="C111" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D111" s="8" t="inlineStr">
+      <c r="D111" s="9" t="inlineStr">
         <is>
           <t>546</t>
         </is>
       </c>
-      <c r="E111" s="8" t="inlineStr">
+      <c r="E111" s="9" t="inlineStr">
         <is>
           <t>Forensics</t>
         </is>
       </c>
-      <c r="F111" s="8" t="inlineStr">
+      <c r="F111" s="9" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="G111" s="8" t="inlineStr">
+      <c r="G111" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H111" s="9" t="n">
+      <c r="H111" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I111" s="9" t="n">
+      <c r="I111" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J111" s="8" t="inlineStr"/>
-      <c r="K111" s="8" t="inlineStr"/>
-      <c r="L111" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M111" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N111" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O111" s="9" t="n">
+      <c r="J111" s="9" t="inlineStr"/>
+      <c r="K111" s="9" t="inlineStr"/>
+      <c r="L111" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M111" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N111" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O111" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -7982,61 +8199,61 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="8" t="inlineStr">
+      <c r="A113" s="9" t="inlineStr">
         <is>
           <t>106323</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B113" s="9" t="inlineStr">
         <is>
           <t>Gebert, Evan</t>
         </is>
       </c>
-      <c r="C113" s="8" t="n">
+      <c r="C113" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D113" s="8" t="inlineStr">
+      <c r="D113" s="9" t="inlineStr">
         <is>
           <t>849</t>
         </is>
       </c>
-      <c r="E113" s="8" t="inlineStr">
+      <c r="E113" s="9" t="inlineStr">
         <is>
           <t>Catholic Social Teaching</t>
         </is>
       </c>
-      <c r="F113" s="8" t="inlineStr">
+      <c r="F113" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="G113" s="8" t="inlineStr">
+      <c r="G113" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H113" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I113" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J113" s="8" t="inlineStr">
+      <c r="H113" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I113" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J113" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="K113" s="8" t="inlineStr"/>
-      <c r="L113" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M113" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N113" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O113" s="9" t="n">
+      <c r="K113" s="9" t="inlineStr"/>
+      <c r="L113" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M113" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N113" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O113" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -8100,57 +8317,57 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="8" t="inlineStr">
+      <c r="A115" s="9" t="inlineStr">
         <is>
           <t>112088</t>
         </is>
       </c>
-      <c r="B115" s="8" t="inlineStr">
+      <c r="B115" s="9" t="inlineStr">
         <is>
           <t>Helou, Ramsey</t>
         </is>
       </c>
-      <c r="C115" s="8" t="n">
+      <c r="C115" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D115" s="8" t="inlineStr">
+      <c r="D115" s="9" t="inlineStr">
         <is>
           <t>708</t>
         </is>
       </c>
-      <c r="E115" s="8" t="inlineStr">
+      <c r="E115" s="9" t="inlineStr">
         <is>
           <t>Introduction to Business</t>
         </is>
       </c>
-      <c r="F115" s="8" t="inlineStr">
+      <c r="F115" s="9" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="G115" s="8" t="inlineStr">
+      <c r="G115" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H115" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I115" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J115" s="8" t="inlineStr"/>
-      <c r="K115" s="8" t="inlineStr"/>
-      <c r="L115" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M115" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N115" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O115" s="9" t="n">
+      <c r="H115" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I115" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J115" s="9" t="inlineStr"/>
+      <c r="K115" s="9" t="inlineStr"/>
+      <c r="L115" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M115" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N115" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O115" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -8210,57 +8427,57 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="8" t="inlineStr">
+      <c r="A117" s="9" t="inlineStr">
         <is>
           <t>112088</t>
         </is>
       </c>
-      <c r="B117" s="8" t="inlineStr">
+      <c r="B117" s="9" t="inlineStr">
         <is>
           <t>Helou, Ramsey</t>
         </is>
       </c>
-      <c r="C117" s="8" t="n">
+      <c r="C117" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D117" s="8" t="inlineStr">
+      <c r="D117" s="9" t="inlineStr">
         <is>
           <t>2044</t>
         </is>
       </c>
-      <c r="E117" s="8" t="inlineStr">
+      <c r="E117" s="9" t="inlineStr">
         <is>
           <t>TV/Film Production II</t>
         </is>
       </c>
-      <c r="F117" s="8" t="inlineStr">
+      <c r="F117" s="9" t="inlineStr">
         <is>
           <t>Communication Arts</t>
         </is>
       </c>
-      <c r="G117" s="8" t="inlineStr">
+      <c r="G117" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H117" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I117" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J117" s="8" t="inlineStr"/>
-      <c r="K117" s="8" t="inlineStr"/>
-      <c r="L117" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M117" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N117" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O117" s="9" t="n">
+      <c r="H117" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I117" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J117" s="9" t="inlineStr"/>
+      <c r="K117" s="9" t="inlineStr"/>
+      <c r="L117" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M117" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N117" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O117" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -8320,61 +8537,61 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="8" t="inlineStr">
+      <c r="A119" s="9" t="inlineStr">
         <is>
           <t>112088</t>
         </is>
       </c>
-      <c r="B119" s="8" t="inlineStr">
+      <c r="B119" s="9" t="inlineStr">
         <is>
           <t>Helou, Ramsey</t>
         </is>
       </c>
-      <c r="C119" s="8" t="n">
+      <c r="C119" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D119" s="8" t="inlineStr">
+      <c r="D119" s="9" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="E119" s="8" t="inlineStr">
+      <c r="E119" s="9" t="inlineStr">
         <is>
           <t>College English Honors</t>
         </is>
       </c>
-      <c r="F119" s="8" t="inlineStr">
+      <c r="F119" s="9" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="G119" s="8" t="inlineStr">
+      <c r="G119" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H119" s="9" t="n">
+      <c r="H119" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I119" s="9" t="n">
+      <c r="I119" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J119" s="8" t="inlineStr">
+      <c r="J119" s="9" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="K119" s="8" t="inlineStr"/>
-      <c r="L119" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M119" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N119" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O119" s="9" t="n">
+      <c r="K119" s="9" t="inlineStr"/>
+      <c r="L119" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M119" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N119" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O119" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -8434,57 +8651,57 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="8" t="inlineStr">
+      <c r="A121" s="9" t="inlineStr">
         <is>
           <t>112088</t>
         </is>
       </c>
-      <c r="B121" s="8" t="inlineStr">
+      <c r="B121" s="9" t="inlineStr">
         <is>
           <t>Helou, Ramsey</t>
         </is>
       </c>
-      <c r="C121" s="8" t="n">
+      <c r="C121" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D121" s="8" t="inlineStr">
+      <c r="D121" s="9" t="inlineStr">
         <is>
           <t>144</t>
         </is>
       </c>
-      <c r="E121" s="8" t="inlineStr">
+      <c r="E121" s="9" t="inlineStr">
         <is>
           <t>Public Speaking</t>
         </is>
       </c>
-      <c r="F121" s="8" t="inlineStr">
+      <c r="F121" s="9" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="G121" s="8" t="inlineStr">
+      <c r="G121" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H121" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I121" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J121" s="8" t="inlineStr"/>
-      <c r="K121" s="8" t="inlineStr"/>
-      <c r="L121" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M121" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N121" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O121" s="9" t="n">
+      <c r="H121" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I121" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J121" s="9" t="inlineStr"/>
+      <c r="K121" s="9" t="inlineStr"/>
+      <c r="L121" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M121" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N121" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O121" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -8548,57 +8765,57 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="8" t="inlineStr">
+      <c r="A123" s="9" t="inlineStr">
         <is>
           <t>112088</t>
         </is>
       </c>
-      <c r="B123" s="8" t="inlineStr">
+      <c r="B123" s="9" t="inlineStr">
         <is>
           <t>Helou, Ramsey</t>
         </is>
       </c>
-      <c r="C123" s="8" t="n">
+      <c r="C123" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D123" s="8" t="inlineStr">
+      <c r="D123" s="9" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="E123" s="8" t="inlineStr">
+      <c r="E123" s="9" t="inlineStr">
         <is>
           <t>Psychology</t>
         </is>
       </c>
-      <c r="F123" s="8" t="inlineStr">
+      <c r="F123" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="G123" s="8" t="inlineStr">
+      <c r="G123" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H123" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I123" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J123" s="8" t="inlineStr"/>
-      <c r="K123" s="8" t="inlineStr"/>
-      <c r="L123" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M123" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N123" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O123" s="9" t="n">
+      <c r="H123" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I123" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J123" s="9" t="inlineStr"/>
+      <c r="K123" s="9" t="inlineStr"/>
+      <c r="L123" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M123" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N123" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O123" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -8662,61 +8879,61 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="8" t="inlineStr">
+      <c r="A125" s="9" t="inlineStr">
         <is>
           <t>112088</t>
         </is>
       </c>
-      <c r="B125" s="8" t="inlineStr">
+      <c r="B125" s="9" t="inlineStr">
         <is>
           <t>Helou, Ramsey</t>
         </is>
       </c>
-      <c r="C125" s="8" t="n">
+      <c r="C125" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D125" s="8" t="inlineStr">
+      <c r="D125" s="9" t="inlineStr">
         <is>
           <t>851</t>
         </is>
       </c>
-      <c r="E125" s="8" t="inlineStr">
+      <c r="E125" s="9" t="inlineStr">
         <is>
           <t>Spirituality of Vocation</t>
         </is>
       </c>
-      <c r="F125" s="8" t="inlineStr">
+      <c r="F125" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="G125" s="8" t="inlineStr">
+      <c r="G125" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H125" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I125" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J125" s="8" t="inlineStr">
+      <c r="H125" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I125" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J125" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="K125" s="8" t="inlineStr"/>
-      <c r="L125" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M125" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N125" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O125" s="9" t="n">
+      <c r="K125" s="9" t="inlineStr"/>
+      <c r="L125" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M125" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N125" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O125" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -8776,57 +8993,57 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="8" t="inlineStr">
+      <c r="A127" s="9" t="inlineStr">
         <is>
           <t>106216</t>
         </is>
       </c>
-      <c r="B127" s="8" t="inlineStr">
+      <c r="B127" s="9" t="inlineStr">
         <is>
           <t>McLaughlin, Sean</t>
         </is>
       </c>
-      <c r="C127" s="8" t="n">
+      <c r="C127" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D127" s="8" t="inlineStr">
+      <c r="D127" s="9" t="inlineStr">
         <is>
           <t>757</t>
         </is>
       </c>
-      <c r="E127" s="8" t="inlineStr">
+      <c r="E127" s="9" t="inlineStr">
         <is>
           <t>International Business Strategies</t>
         </is>
       </c>
-      <c r="F127" s="8" t="inlineStr">
+      <c r="F127" s="9" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="G127" s="8" t="inlineStr">
+      <c r="G127" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H127" s="9" t="n">
+      <c r="H127" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I127" s="9" t="n">
+      <c r="I127" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J127" s="8" t="inlineStr"/>
-      <c r="K127" s="8" t="inlineStr"/>
-      <c r="L127" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M127" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N127" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O127" s="9" t="n">
+      <c r="J127" s="9" t="inlineStr"/>
+      <c r="K127" s="9" t="inlineStr"/>
+      <c r="L127" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M127" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N127" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O127" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -8890,61 +9107,61 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="8" t="inlineStr">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>106216</t>
         </is>
       </c>
-      <c r="B129" s="8" t="inlineStr">
+      <c r="B129" s="9" t="inlineStr">
         <is>
           <t>McLaughlin, Sean</t>
         </is>
       </c>
-      <c r="C129" s="8" t="n">
+      <c r="C129" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D129" s="8" t="inlineStr">
+      <c r="D129" s="9" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E129" s="8" t="inlineStr">
+      <c r="E129" s="9" t="inlineStr">
         <is>
           <t>AP Precalculus</t>
         </is>
       </c>
-      <c r="F129" s="8" t="inlineStr">
+      <c r="F129" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="G129" s="8" t="inlineStr">
+      <c r="G129" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H129" s="9" t="n">
+      <c r="H129" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I129" s="9" t="n">
+      <c r="I129" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J129" s="8" t="inlineStr">
+      <c r="J129" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="K129" s="8" t="inlineStr"/>
-      <c r="L129" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M129" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N129" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O129" s="9" t="n">
+      <c r="K129" s="9" t="inlineStr"/>
+      <c r="L129" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M129" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N129" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O129" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -9004,61 +9221,61 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="8" t="inlineStr">
+      <c r="A131" s="9" t="inlineStr">
         <is>
           <t>106216</t>
         </is>
       </c>
-      <c r="B131" s="8" t="inlineStr">
+      <c r="B131" s="9" t="inlineStr">
         <is>
           <t>McLaughlin, Sean</t>
         </is>
       </c>
-      <c r="C131" s="8" t="n">
+      <c r="C131" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D131" s="8" t="inlineStr">
+      <c r="D131" s="9" t="inlineStr">
         <is>
           <t>557</t>
         </is>
       </c>
-      <c r="E131" s="8" t="inlineStr">
+      <c r="E131" s="9" t="inlineStr">
         <is>
           <t>AP Physics 1</t>
         </is>
       </c>
-      <c r="F131" s="8" t="inlineStr">
+      <c r="F131" s="9" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="G131" s="8" t="inlineStr">
+      <c r="G131" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H131" s="9" t="n">
+      <c r="H131" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I131" s="9" t="n">
+      <c r="I131" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J131" s="8" t="inlineStr">
+      <c r="J131" s="9" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="K131" s="8" t="inlineStr"/>
-      <c r="L131" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M131" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N131" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O131" s="9" t="n">
+      <c r="K131" s="9" t="inlineStr"/>
+      <c r="L131" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M131" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N131" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O131" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -9122,61 +9339,61 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="8" t="inlineStr">
+      <c r="A133" s="9" t="inlineStr">
         <is>
           <t>106216</t>
         </is>
       </c>
-      <c r="B133" s="8" t="inlineStr">
+      <c r="B133" s="9" t="inlineStr">
         <is>
           <t>McLaughlin, Sean</t>
         </is>
       </c>
-      <c r="C133" s="8" t="n">
+      <c r="C133" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D133" s="8" t="inlineStr">
+      <c r="D133" s="9" t="inlineStr">
         <is>
           <t>851</t>
         </is>
       </c>
-      <c r="E133" s="8" t="inlineStr">
+      <c r="E133" s="9" t="inlineStr">
         <is>
           <t>Spirituality of Vocation</t>
         </is>
       </c>
-      <c r="F133" s="8" t="inlineStr">
+      <c r="F133" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="G133" s="8" t="inlineStr">
+      <c r="G133" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H133" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I133" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J133" s="8" t="inlineStr">
+      <c r="H133" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I133" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J133" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="K133" s="8" t="inlineStr"/>
-      <c r="L133" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M133" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N133" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O133" s="9" t="n">
+      <c r="K133" s="9" t="inlineStr"/>
+      <c r="L133" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M133" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N133" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O133" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -9240,61 +9457,61 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="8" t="inlineStr">
+      <c r="A135" s="9" t="inlineStr">
         <is>
           <t>106232</t>
         </is>
       </c>
-      <c r="B135" s="8" t="inlineStr">
+      <c r="B135" s="9" t="inlineStr">
         <is>
           <t>Nadler, Nathaniel</t>
         </is>
       </c>
-      <c r="C135" s="8" t="n">
+      <c r="C135" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D135" s="8" t="inlineStr">
+      <c r="D135" s="9" t="inlineStr">
         <is>
           <t>763</t>
         </is>
       </c>
-      <c r="E135" s="8" t="inlineStr">
+      <c r="E135" s="9" t="inlineStr">
         <is>
           <t>AP U.S. Government &amp; Politics</t>
         </is>
       </c>
-      <c r="F135" s="8" t="inlineStr">
+      <c r="F135" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="G135" s="8" t="inlineStr">
+      <c r="G135" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H135" s="9" t="n">
+      <c r="H135" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I135" s="9" t="n">
+      <c r="I135" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J135" s="8" t="inlineStr">
+      <c r="J135" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="K135" s="8" t="inlineStr"/>
-      <c r="L135" s="9" t="n">
+      <c r="K135" s="9" t="inlineStr"/>
+      <c r="L135" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="M135" s="9" t="n">
+      <c r="M135" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="N135" s="9" t="n">
+      <c r="N135" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="O135" s="9" t="n">
+      <c r="O135" s="10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9358,61 +9575,61 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="8" t="inlineStr">
+      <c r="A137" s="9" t="inlineStr">
         <is>
           <t>106232</t>
         </is>
       </c>
-      <c r="B137" s="8" t="inlineStr">
+      <c r="B137" s="9" t="inlineStr">
         <is>
           <t>Nadler, Nathaniel</t>
         </is>
       </c>
-      <c r="C137" s="8" t="n">
+      <c r="C137" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D137" s="8" t="inlineStr">
+      <c r="D137" s="9" t="inlineStr">
         <is>
           <t>851</t>
         </is>
       </c>
-      <c r="E137" s="8" t="inlineStr">
+      <c r="E137" s="9" t="inlineStr">
         <is>
           <t>Spirituality of Vocation</t>
         </is>
       </c>
-      <c r="F137" s="8" t="inlineStr">
+      <c r="F137" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="G137" s="8" t="inlineStr">
+      <c r="G137" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H137" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I137" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J137" s="8" t="inlineStr">
+      <c r="H137" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I137" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J137" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="K137" s="8" t="inlineStr"/>
-      <c r="L137" s="9" t="n">
+      <c r="K137" s="9" t="inlineStr"/>
+      <c r="L137" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="M137" s="9" t="n">
+      <c r="M137" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="N137" s="9" t="n">
+      <c r="N137" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="O137" s="9" t="n">
+      <c r="O137" s="10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9476,61 +9693,61 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="8" t="inlineStr">
+      <c r="A139" s="9" t="inlineStr">
         <is>
           <t>106248</t>
         </is>
       </c>
-      <c r="B139" s="8" t="inlineStr">
+      <c r="B139" s="9" t="inlineStr">
         <is>
           <t>Strayton, Ryder</t>
         </is>
       </c>
-      <c r="C139" s="8" t="n">
+      <c r="C139" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D139" s="8" t="inlineStr">
+      <c r="D139" s="9" t="inlineStr">
         <is>
           <t>440</t>
         </is>
       </c>
-      <c r="E139" s="8" t="inlineStr">
+      <c r="E139" s="9" t="inlineStr">
         <is>
           <t>Precalculus</t>
         </is>
       </c>
-      <c r="F139" s="8" t="inlineStr">
+      <c r="F139" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="G139" s="8" t="inlineStr">
+      <c r="G139" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="H139" s="9" t="n">
+      <c r="H139" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I139" s="9" t="n">
+      <c r="I139" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J139" s="8" t="inlineStr">
+      <c r="J139" s="9" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="K139" s="8" t="inlineStr"/>
-      <c r="L139" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M139" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N139" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O139" s="9" t="n">
+      <c r="K139" s="9" t="inlineStr"/>
+      <c r="L139" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M139" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N139" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O139" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -9590,61 +9807,61 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="8" t="inlineStr">
+      <c r="A141" s="9" t="inlineStr">
         <is>
           <t>106248</t>
         </is>
       </c>
-      <c r="B141" s="8" t="inlineStr">
+      <c r="B141" s="9" t="inlineStr">
         <is>
           <t>Strayton, Ryder</t>
         </is>
       </c>
-      <c r="C141" s="8" t="n">
+      <c r="C141" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D141" s="8" t="inlineStr">
+      <c r="D141" s="9" t="inlineStr">
         <is>
           <t>751</t>
         </is>
       </c>
-      <c r="E141" s="8" t="inlineStr">
+      <c r="E141" s="9" t="inlineStr">
         <is>
           <t>American Government &amp; Politics</t>
         </is>
       </c>
-      <c r="F141" s="8" t="inlineStr">
+      <c r="F141" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="G141" s="8" t="inlineStr">
+      <c r="G141" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H141" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I141" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J141" s="8" t="inlineStr">
+      <c r="H141" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I141" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J141" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="K141" s="8" t="inlineStr"/>
-      <c r="L141" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M141" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N141" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O141" s="9" t="n">
+      <c r="K141" s="9" t="inlineStr"/>
+      <c r="L141" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M141" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N141" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O141" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -9704,57 +9921,57 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="8" t="inlineStr">
+      <c r="A143" s="9" t="inlineStr">
         <is>
           <t>106248</t>
         </is>
       </c>
-      <c r="B143" s="8" t="inlineStr">
+      <c r="B143" s="9" t="inlineStr">
         <is>
           <t>Strayton, Ryder</t>
         </is>
       </c>
-      <c r="C143" s="8" t="n">
+      <c r="C143" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D143" s="8" t="inlineStr">
+      <c r="D143" s="9" t="inlineStr">
         <is>
           <t>756</t>
         </is>
       </c>
-      <c r="E143" s="8" t="inlineStr">
+      <c r="E143" s="9" t="inlineStr">
         <is>
           <t>Introduction to Law</t>
         </is>
       </c>
-      <c r="F143" s="8" t="inlineStr">
+      <c r="F143" s="9" t="inlineStr">
         <is>
           <t>Social Studies</t>
         </is>
       </c>
-      <c r="G143" s="8" t="inlineStr">
+      <c r="G143" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H143" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I143" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J143" s="8" t="inlineStr"/>
-      <c r="K143" s="8" t="inlineStr"/>
-      <c r="L143" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M143" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N143" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O143" s="9" t="n">
+      <c r="H143" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I143" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J143" s="9" t="inlineStr"/>
+      <c r="K143" s="9" t="inlineStr"/>
+      <c r="L143" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M143" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N143" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O143" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -9814,61 +10031,61 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="8" t="inlineStr">
+      <c r="A145" s="9" t="inlineStr">
         <is>
           <t>106248</t>
         </is>
       </c>
-      <c r="B145" s="8" t="inlineStr">
+      <c r="B145" s="9" t="inlineStr">
         <is>
           <t>Strayton, Ryder</t>
         </is>
       </c>
-      <c r="C145" s="8" t="n">
+      <c r="C145" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D145" s="8" t="inlineStr">
+      <c r="D145" s="9" t="inlineStr">
         <is>
           <t>849</t>
         </is>
       </c>
-      <c r="E145" s="8" t="inlineStr">
+      <c r="E145" s="9" t="inlineStr">
         <is>
           <t>Catholic Social Teaching</t>
         </is>
       </c>
-      <c r="F145" s="8" t="inlineStr">
+      <c r="F145" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="G145" s="8" t="inlineStr">
+      <c r="G145" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H145" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I145" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J145" s="8" t="inlineStr">
+      <c r="H145" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I145" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J145" s="9" t="inlineStr">
         <is>
           <t>Theology</t>
         </is>
       </c>
-      <c r="K145" s="8" t="inlineStr"/>
-      <c r="L145" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="M145" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N145" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O145" s="9" t="n">
+      <c r="K145" s="9" t="inlineStr"/>
+      <c r="L145" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="M145" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N145" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O145" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -9942,7 +10159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9953,7 +10170,9 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="31" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="53" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
+    <col width="58" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9999,6 +10218,16 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Prev Year World Language</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Prev Year Elective</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -10017,7 +10246,7 @@
       <c r="C2" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="20" t="inlineStr">
         <is>
           <t>Elective / PE / Arts</t>
         </is>
@@ -10040,46 +10269,66 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
           <t>All core subjects present. Missing 1 semester elective (0.5 slot / 2.5 credits)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>121287</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Elliott, Michael</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>Elective / PE / Arts</t>
         </is>
       </c>
-      <c r="E3" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="E3" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G3" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="G3" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
         <is>
           <t>All core subjects present. Missing 1 semester elective (0.5 slot / 2.5 credits)</t>
         </is>
@@ -10099,7 +10348,7 @@
       <c r="C4" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Elective / PE / Arts</t>
         </is>
@@ -10122,46 +10371,66 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
           <t>All core subjects present. Missing 1 semester elective (0.5 slot / 2.5 credits)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>109385</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Saliba, Georges</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>Physical Education</t>
         </is>
       </c>
-      <c r="E5" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="E5" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G5" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="G5" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>YES — Graduation Required</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr"/>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -10177,7 +10446,7 @@
       <c r="C6" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Elective / PE / Arts</t>
         </is>
@@ -10200,46 +10469,66 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
           <t>All core subjects present. Missing 1 semester elective (0.5 slot / 2.5 credits)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>121949</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Ferko, Lavdosh</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>Elective / PE / Arts</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="E7" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G7" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="G7" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="K7" s="12" t="inlineStr">
         <is>
           <t>All core subjects present. Missing 1 semester elective (0.5 slot / 2.5 credits)</t>
         </is>
@@ -10259,7 +10548,7 @@
       <c r="C8" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>World Language</t>
         </is>
@@ -10275,49 +10564,69 @@
       <c r="G8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>YES — Graduation Required</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>121320</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Kirby, Benjamin</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>World Language</t>
         </is>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>YES — Graduation Required</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr"/>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -10333,7 +10642,7 @@
       <c r="C10" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>Elective / PE / Arts</t>
         </is>
@@ -10356,46 +10665,66 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
           <t>All core subjects present. Missing 1 semester elective (0.5 slot / 2.5 credits)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>108153</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Vagnone, Tyler</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>Elective / PE / Arts</t>
         </is>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E11" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G11" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="G11" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
         <is>
           <t>All core subjects present. Missing 1 semester elective (0.5 slot / 2.5 credits)</t>
         </is>
@@ -10415,7 +10744,7 @@
       <c r="C12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>Elective / PE / Arts</t>
         </is>
@@ -10438,46 +10767,66 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
           <t>All core subjects present. Missing 1 semester elective (0.5 slot / 2.5 credits)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>106291</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Bonita, Andrew</t>
         </is>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>Elective / PE / Arts</t>
         </is>
       </c>
-      <c r="E13" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="E13" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G13" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="G13" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>333 Italian III H</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="inlineStr">
         <is>
           <t>All core subjects present. Missing 1 semester elective (0.5 slot / 2.5 credits)</t>
         </is>
@@ -10497,7 +10846,7 @@
       <c r="C14" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>Elective / PE / Arts</t>
         </is>
@@ -10520,46 +10869,66 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
+          <t>332 Italian III</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
           <t>All core subjects present. Missing 1 semester elective (0.5 slot / 2.5 credits)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>106243</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Duran, Nicholas</t>
         </is>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>Elective / PE / Arts</t>
         </is>
       </c>
-      <c r="E15" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="E15" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G15" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="G15" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>330 Spanish III</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>2054 Digital Media</t>
+        </is>
+      </c>
+      <c r="K15" s="12" t="inlineStr">
         <is>
           <t>All core subjects present. Missing 1 semester elective (0.5 slot / 2.5 credits)</t>
         </is>
@@ -10579,7 +10948,7 @@
       <c r="C16" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>Elective / PE / Arts</t>
         </is>
@@ -10602,46 +10971,66 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
+          <t>330 Spanish III</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
           <t>All core subjects present. Missing 1 semester elective (0.5 slot / 2.5 credits)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>112088</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Helou, Ramsey</t>
         </is>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>Elective / PE / Arts</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="E17" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G17" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="G17" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>2034 TV/Film Production &amp; Editing I</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="inlineStr">
         <is>
           <t>All core subjects present. Missing 1 semester elective (0.5 slot / 2.5 credits)</t>
         </is>
@@ -10661,7 +11050,7 @@
       <c r="C18" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>Elective / PE / Arts</t>
         </is>
@@ -10684,46 +11073,66 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
+          <t>331 Spanish III H</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
           <t>All core subjects present. Missing 1 semester elective (0.5 slot / 2.5 credits)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>106232</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Nadler, Nathaniel</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="H19" s="15" t="inlineStr">
         <is>
           <t>YES — Graduation Required</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr"/>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>351 AP Spanish</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>490 AP Computer Science A</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -10739,7 +11148,7 @@
       <c r="C20" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>Elective / PE / Arts</t>
         </is>
@@ -10761,6 +11170,16 @@
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>No historical data</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>All core subjects present. Missing 1 semester elective (0.5 slot / 2.5 credits)</t>
         </is>
@@ -10777,7 +11196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -10803,309 +11222,368 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>UNDER-ENROLLED STUDENTS</t>
         </is>
       </c>
-      <c r="B2" s="19" t="n">
+      <c r="B2" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="C2" s="20" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>Students with fewer than 7 period slots filled</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr"/>
-      <c r="B3" s="19" t="inlineStr"/>
-      <c r="C3" s="20" t="inlineStr"/>
+      <c r="A3" s="23" t="inlineStr"/>
+      <c r="B3" s="23" t="inlineStr"/>
+      <c r="C3" s="14" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>── By Grade ──</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr"/>
-      <c r="C4" s="20" t="inlineStr"/>
+      <c r="B4" s="23" t="inlineStr"/>
+      <c r="C4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Grade 9</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
+      <c r="B5" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="20" t="inlineStr"/>
+      <c r="C5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Grade 10</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
+      <c r="B6" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
+      <c r="C6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Grade 11</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="20" t="inlineStr"/>
+      <c r="C7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Grade 12</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="C8" s="20" t="inlineStr"/>
+      <c r="C8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr"/>
-      <c r="B9" s="19" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr"/>
+      <c r="A9" s="23" t="inlineStr"/>
+      <c r="B9" s="23" t="inlineStr"/>
+      <c r="C9" s="14" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>── By Deficit Size ──</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr"/>
+      <c r="B10" s="23" t="inlineStr"/>
+      <c r="C10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Missing 0.5 slot (1 semester)</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n">
+      <c r="B11" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>2.5 credits missing</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Missing 1.0 slot (1 full-year)</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n">
+      <c r="B12" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>5.0 credits missing</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Missing &gt; 1.0 slots</t>
         </is>
       </c>
-      <c r="B13" s="19" t="n">
+      <c r="B13" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Multiple courses missing</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr"/>
-      <c r="B14" s="19" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr"/>
+      <c r="A14" s="23" t="inlineStr"/>
+      <c r="B14" s="23" t="inlineStr"/>
+      <c r="C14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>── By Root Cause ──</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr"/>
-      <c r="C15" s="20" t="inlineStr"/>
+      <c r="B15" s="23" t="inlineStr"/>
+      <c r="C15" s="14" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Missing core dept/subject</t>
         </is>
       </c>
-      <c r="B16" s="19" t="n">
+      <c r="B16" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>A required graduation department is not covered</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  All core present, missing elective</t>
         </is>
       </c>
-      <c r="B17" s="19" t="n">
+      <c r="B17" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>Needs PE, Arts, or other elective</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr"/>
-      <c r="B18" s="19" t="inlineStr"/>
-      <c r="C18" s="20" t="inlineStr"/>
+      <c r="A18" s="23" t="inlineStr"/>
+      <c r="B18" s="23" t="inlineStr"/>
+      <c r="C18" s="14" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>── Missing Departments ──</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr"/>
-      <c r="C19" s="20" t="inlineStr"/>
+      <c r="B19" s="23" t="inlineStr"/>
+      <c r="C19" s="14" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  World Language</t>
         </is>
       </c>
-      <c r="B20" s="19" t="n">
+      <c r="B20" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>students missing this department</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Physical Education</t>
         </is>
       </c>
-      <c r="B21" s="19" t="n">
+      <c r="B21" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>students missing this department</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Mathematics</t>
         </is>
       </c>
-      <c r="B22" s="19" t="n">
+      <c r="B22" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>students missing this department</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr"/>
-      <c r="B23" s="19" t="inlineStr"/>
-      <c r="C23" s="20" t="inlineStr"/>
+      <c r="A23" s="23" t="inlineStr"/>
+      <c r="B23" s="23" t="inlineStr"/>
+      <c r="C23" s="14" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>── Previous Year History ──</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr"/>
+      <c r="C24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Had World Language (2025-26)</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Took a WL course last year</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Had Elective (2025-26)</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Took a non-core elective last year</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  No historical data</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Not found in Historical Grades template</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr"/>
+      <c r="B28" s="23" t="inlineStr"/>
+      <c r="C28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>── Totals ──</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr"/>
-      <c r="C24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr"/>
+      <c r="C29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total Credits Missing</t>
         </is>
       </c>
-      <c r="B25" s="19" t="n">
+      <c r="B30" s="23" t="n">
         <v>75</v>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>Sum of all credit deficits</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total Slots Missing</t>
         </is>
       </c>
-      <c r="B26" s="19" t="n">
+      <c r="B31" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>Sum of all slot deficits</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Avg Credits Missing</t>
         </is>
       </c>
-      <c r="B27" s="19" t="n">
+      <c r="B32" s="23" t="n">
         <v>3.9</v>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>Per student</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Avg Slots Missing</t>
         </is>
       </c>
-      <c r="B28" s="19" t="n">
+      <c r="B33" s="23" t="n">
         <v>0.8</v>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>Per student</t>
         </is>
